--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.75683296171013</v>
+        <v>7.110485356277897</v>
       </c>
       <c r="D2" t="n">
-        <v>28.21413506252914</v>
+        <v>4.584796947660986</v>
       </c>
       <c r="E2" t="n">
-        <v>12.4534018326509</v>
+        <v>2.023677797805771</v>
       </c>
       <c r="F2" t="n">
-        <v>9.653209920343942</v>
+        <v>1.568646612055891</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.26267650163207</v>
+        <v>2.805184931515211</v>
       </c>
       <c r="D3" t="n">
-        <v>19.69938538814818</v>
+        <v>3.201150125574079</v>
       </c>
       <c r="E3" t="n">
-        <v>12.4534018326509</v>
+        <v>2.023677797805771</v>
       </c>
       <c r="F3" t="n">
-        <v>9.653209920343942</v>
+        <v>1.568646612055891</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.45221926760138</v>
+        <v>7.060985630985225</v>
       </c>
       <c r="D4" t="n">
-        <v>38.89087296526012</v>
+        <v>6.319766856854769</v>
       </c>
       <c r="E4" t="n">
-        <v>12.4534018326509</v>
+        <v>2.023677797805771</v>
       </c>
       <c r="F4" t="n">
-        <v>9.653209920343942</v>
+        <v>1.568646612055891</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.25930184195699</v>
+        <v>2.804636549318011</v>
       </c>
       <c r="D5" t="n">
-        <v>42.13841366309283</v>
+        <v>6.847492220252585</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4534018326509</v>
+        <v>2.023677797805771</v>
       </c>
       <c r="F5" t="n">
-        <v>9.653209920343942</v>
+        <v>1.568646612055891</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.61607546656198</v>
+        <v>2.212612263316322</v>
       </c>
       <c r="D6" t="n">
-        <v>17.92344832893492</v>
+        <v>2.912560353451925</v>
       </c>
       <c r="E6" t="n">
-        <v>12.4534018326509</v>
+        <v>2.023677797805771</v>
       </c>
       <c r="F6" t="n">
-        <v>9.653209920343942</v>
+        <v>1.568646612055891</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.56154585388024</v>
+        <v>3.828751201255539</v>
       </c>
       <c r="D7" t="n">
-        <v>19.60306839735164</v>
+        <v>3.185498614569642</v>
       </c>
       <c r="E7" t="n">
-        <v>12.4534018326509</v>
+        <v>2.023677797805771</v>
       </c>
       <c r="F7" t="n">
-        <v>9.653209920343942</v>
+        <v>1.568646612055891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
